--- a/tests/e2e/fixtures/tpl-real-like.xlsx
+++ b/tests/e2e/fixtures/tpl-real-like.xlsx
@@ -68,7 +68,7 @@
     <t>〒000-0000</t>
   </si>
   <si>
-    <t>○○県○○市中央7-3-40　00コーポ1号</t>
+    <t>東京都架空区見本町1-2-3　00コーポ1号</t>
   </si>
   <si>
     <t>TEL000-0000-0000</t>

--- a/tests/e2e/fixtures/tpl-real-like.xlsx
+++ b/tests/e2e/fixtures/tpl-real-like.xlsx
@@ -68,7 +68,7 @@
     <t>〒000-0000</t>
   </si>
   <si>
-    <t>東京都架空区見本町1-2-3　00コーポ1号</t>
+    <t>東京都架空区見本台1-2-3　00コーポ1号</t>
   </si>
   <si>
     <t>TEL000-0000-0000</t>
